--- a/outputs/402-43.xlsx
+++ b/outputs/402-43.xlsx
@@ -278,20 +278,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -487,701 +491,701 @@
   <dimension ref="A1:AG25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="5" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="9" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="20" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="5" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="9" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="20" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="S2" s="0" t="s">
+      <c r="I2" s="3"/>
+      <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AE2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="0" t="s">
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AE2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="S3" s="0" t="s">
+      <c r="I3" s="3"/>
+      <c r="S3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AE3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF3" s="0" t="s">
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AE3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="0" t="s">
+      <c r="S4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AE4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF4" s="0" t="s">
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AE4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="S5" s="0" t="s">
+      <c r="I5" s="3"/>
+      <c r="S5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AE5" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF5" s="0" t="s">
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AE5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="S6" s="0" t="s">
+      <c r="I6" s="3"/>
+      <c r="S6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AE6" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF6" s="0" t="s">
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AE6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="S7" s="0" t="s">
+      <c r="I7" s="3"/>
+      <c r="S7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AE7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF7" s="0" t="s">
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AE7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="P16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="Q16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="R16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="S16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="T16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="U16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V16" s="1" t="s">
+      <c r="V16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W16" s="1" t="s">
+      <c r="W16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="X16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Y16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z16" s="1" t="s">
+      <c r="Z16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AA16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AB16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AC16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AD16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE16" s="1" t="s">
+      <c r="AE16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AF16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG16" s="1" t="s">
+      <c r="AG16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="S17" s="0" t="s">
+      <c r="I17" s="3"/>
+      <c r="S17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AE17" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF17" s="0" t="s">
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AE17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG17" s="0" t="n">
+      <c r="AG17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="0" t="s">
+      <c r="H18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="S18" s="0" t="s">
+      <c r="I18" s="3"/>
+      <c r="S18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AE18" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF18" s="0" t="s">
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AE18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG18" s="0" t="n">
+      <c r="AG18" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="0" t="n">
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="0" t="s">
+      <c r="H19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S19" s="0" t="s">
+      <c r="S19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AE19" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF19" s="0" t="s">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AE19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG19" s="0" t="n">
+      <c r="AG19" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="0" t="n">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="0" t="s">
+      <c r="H20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S20" s="0" t="s">
+      <c r="S20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AE20" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF20" s="0" t="s">
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AE20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG20" s="0" t="n">
+      <c r="AG20" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="0" t="n">
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="0" t="s">
+      <c r="H21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="S21" s="0" t="s">
+      <c r="I21" s="3"/>
+      <c r="S21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AE21" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF21" s="0" t="s">
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AE21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG21" s="0" t="n">
+      <c r="AG21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="0" t="n">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H22" s="0" t="s">
+      <c r="H22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="S22" s="0" t="s">
+      <c r="I22" s="3"/>
+      <c r="S22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AE22" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF22" s="0" t="s">
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AE22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG22" s="0" t="n">
+      <c r="AG22" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="0" t="n">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="S23" s="0" t="s">
+      <c r="I23" s="3"/>
+      <c r="S23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AE23" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF23" s="0" t="s">
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AE23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG23" s="0" t="n">
+      <c r="AG23" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="H24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="S24" s="0" t="s">
+      <c r="I24" s="3"/>
+      <c r="S24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AE24" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF24" s="0" t="s">
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AE24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG24" s="0" t="n">
+      <c r="AG24" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="0" t="n">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="0" t="s">
+      <c r="H25" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="2"/>
-      <c r="S25" s="0" t="s">
+      <c r="I25" s="3"/>
+      <c r="S25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AE25" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF25" s="0" t="s">
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AE25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG25" s="0" t="n">
+      <c r="AG25" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1205,364 +1209,364 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="0" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="0" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF3" s="0" t="s">
+      <c r="AE3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="0" t="s">
+      <c r="S4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF4" s="0" t="s">
+      <c r="AE4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S5" s="0" t="s">
+      <c r="S5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE5" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF5" s="0" t="s">
+      <c r="AE5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>2694091</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S6" s="0" t="s">
+      <c r="S6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AE6" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF6" s="0" t="s">
+      <c r="AE6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="0" t="s">
+      <c r="S7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE7" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF7" s="0" t="s">
+      <c r="AE7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="0" t="s">
+      <c r="S8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE8" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF8" s="0" t="s">
+      <c r="AE8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S9" s="0" t="s">
+      <c r="S9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF9" s="0" t="s">
+      <c r="AE9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>10099841</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S10" s="0" t="s">
+      <c r="S10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE10" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF10" s="0" t="s">
+      <c r="AE10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
         <v>2</v>
       </c>
     </row>

--- a/outputs/402-43.xlsx
+++ b/outputs/402-43.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="53">
   <si>
     <t xml:space="preserve">Col1</t>
   </si>
@@ -1205,7 +1205,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1305,9 +1305,6 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1334,9 +1331,6 @@
       <c r="AF2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
@@ -1363,9 +1357,6 @@
       <c r="AF3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -1392,9 +1383,6 @@
       <c r="AF4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG4" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -1421,9 +1409,6 @@
       <c r="AF5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG5" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -1450,9 +1435,6 @@
       <c r="AF6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG6" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -1479,9 +1461,6 @@
       <c r="AF7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG7" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -1508,9 +1487,6 @@
       <c r="AF8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AG8" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -1537,9 +1513,6 @@
       <c r="AF9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AG9" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
@@ -1565,9 +1538,6 @@
       </c>
       <c r="AF10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="AG10" s="1" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
